--- a/scratch/audit_report.xlsx
+++ b/scratch/audit_report.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T15:55:01.508520</t>
+          <t>2026-10-09T14:08:03.944960</t>
         </is>
       </c>
     </row>
